--- a/data/trans_orig/P21D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>61406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106470</t>
+          <t>107671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165497</t>
+          <t>164469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190215</t>
+          <t>190595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279043</t>
+          <t>280558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300513</t>
+          <t>301693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451218</t>
+          <t>451420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483149</t>
+          <t>484795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -956,82 +956,82 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>12071</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5766</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10073</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
           <t>10227</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5766</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2983</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10357</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>10227</t>
-        </is>
-      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3512</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118199</t>
+          <t>117542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>309325</t>
+          <t>306742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178857</t>
+          <t>178324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>384820</t>
+          <t>416662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>336507</t>
+          <t>333625</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>617386</t>
+          <t>629831</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>787925</t>
+          <t>790532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>989399</t>
+          <t>990896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>536531</t>
+          <t>510537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>739657</t>
+          <t>741137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1412259</t>
+          <t>1396745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1692530</t>
+          <t>1697084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46538</t>
+          <t>46662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,82 +1638,82 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3820</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88376</t>
+          <t>87712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47953</t>
+          <t>49701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>75868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112193</t>
+          <t>114127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155480</t>
+          <t>155744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213127</t>
+          <t>212736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>245218</t>
+          <t>246102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>225789</t>
+          <t>226276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>254045</t>
+          <t>253712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>445499</t>
+          <t>449219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>491652</t>
+          <t>492385</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214378</t>
+          <t>211901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>426128</t>
+          <t>423934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>280052</t>
+          <t>276722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>530583</t>
+          <t>541375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>558469</t>
+          <t>543286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>850878</t>
+          <t>845645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1201607</t>
+          <t>1200449</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1430060</t>
+          <t>1424546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1026918</t>
+          <t>1016004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1273233</t>
+          <t>1276060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2340331</t>
+          <t>2347960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2643181</t>
+          <t>2658984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43578</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>81892</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -2776,82 +2776,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4200</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4969</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">

--- a/data/trans_orig/P21D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61406</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40399</t>
+          <t>43771</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>34585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51535</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>88497</t>
+          <t>105081</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74576</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107671</t>
+          <t>124801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>178319</t>
+          <t>187853</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164469</t>
+          <t>170922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>202439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291082</t>
+          <t>313880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280558</t>
+          <t>301970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301693</t>
+          <t>323978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>469401</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451420</t>
+          <t>481457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484795</t>
+          <t>519086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231247</t>
+          <t>271367</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117542</t>
+          <t>236195</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>306742</t>
+          <t>306364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241966</t>
+          <t>203129</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178324</t>
+          <t>179425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>416662</t>
+          <t>231670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>473213</t>
+          <t>474496</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>333625</t>
+          <t>433492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>629831</t>
+          <t>519412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>871194</t>
+          <t>672168</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>790532</t>
+          <t>637528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>990896</t>
+          <t>707656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>678160</t>
+          <t>763599</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>510537</t>
+          <t>734167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>741137</t>
+          <t>786933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1549354</t>
+          <t>1435768</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1396745</t>
+          <t>1390682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1697084</t>
+          <t>1477885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46662</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71009</t>
+          <t>80653</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55610</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87712</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61758</t>
+          <t>66065</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49701</t>
+          <t>52501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75868</t>
+          <t>80877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>132767</t>
+          <t>146717</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114127</t>
+          <t>123423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155744</t>
+          <t>169960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>230585</t>
+          <t>256204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>212736</t>
+          <t>231736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>246102</t>
+          <t>272279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>266138</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>226276</t>
+          <t>250785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>253712</t>
+          <t>280537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>471508</t>
+          <t>522341</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>449219</t>
+          <t>496948</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>492385</t>
+          <t>544883</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>23188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>350354</t>
+          <t>413330</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211901</t>
+          <t>371248</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>423934</t>
+          <t>456678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>344124</t>
+          <t>312964</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276722</t>
+          <t>281771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>541375</t>
+          <t>344942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>694477</t>
+          <t>726294</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>543286</t>
+          <t>667116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>845645</t>
+          <t>780293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1280098</t>
+          <t>1116225</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1200449</t>
+          <t>1069104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1424546</t>
+          <t>1155109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1210164</t>
+          <t>1343616</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1016004</t>
+          <t>1311275</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1276060</t>
+          <t>1377264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2490262</t>
+          <t>2459842</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2347960</t>
+          <t>2403982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2658984</t>
+          <t>2515310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>50329</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>81892</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
